--- a/datos/catalogo.xlsx
+++ b/datos/catalogo.xlsx
@@ -1214,6 +1214,7 @@
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="6" width="9.5703125" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" customWidth="1"/>
@@ -1259,7 +1260,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -1282,7 +1283,7 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -1305,7 +1306,7 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -1328,7 +1329,7 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
@@ -1351,7 +1352,7 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1374,7 +1375,7 @@
         <v>11</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
         <v>32</v>
@@ -1440,7 +1441,7 @@
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1486,10 +1487,10 @@
         <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
         <v>50</v>
@@ -1512,7 +1513,7 @@
         <v>11</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -1535,7 +1536,7 @@
         <v>11</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="s">
         <v>56</v>
@@ -1555,7 +1556,7 @@
         <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1604,7 +1605,7 @@
         <v>11</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="s">
         <v>66</v>
@@ -1627,7 +1628,7 @@
         <v>11</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="s">
         <v>69</v>
@@ -1673,7 +1674,7 @@
         <v>11</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G20" t="s">
         <v>75</v>
@@ -1696,7 +1697,7 @@
         <v>11</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="s">
         <v>78</v>
@@ -1719,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" t="s">
         <v>81</v>
@@ -1739,7 +1740,7 @@
         <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1765,7 +1766,7 @@
         <v>11</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
         <v>87</v>
@@ -1811,7 +1812,7 @@
         <v>11</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G26" t="s">
         <v>93</v>
@@ -1834,7 +1835,7 @@
         <v>11</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="s">
         <v>96</v>
@@ -1857,7 +1858,7 @@
         <v>11</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G28" t="s">
         <v>99</v>
@@ -1880,7 +1881,7 @@
         <v>11</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
         <v>102</v>
@@ -1903,7 +1904,7 @@
         <v>11</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
         <v>105</v>
@@ -1949,7 +1950,7 @@
         <v>11</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
         <v>112</v>
@@ -1969,7 +1970,7 @@
         <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1995,7 +1996,7 @@
         <v>11</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -2018,7 +2019,7 @@
         <v>11</v>
       </c>
       <c r="F35">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G35" t="s">
         <v>121</v>
@@ -2038,7 +2039,7 @@
         <v>124</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2064,7 +2065,7 @@
         <v>11</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G37" t="s">
         <v>128</v>
@@ -2087,7 +2088,7 @@
         <v>11</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" t="s">
         <v>131</v>
@@ -2110,7 +2111,7 @@
         <v>11</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G39" t="s">
         <v>134</v>
@@ -2133,7 +2134,7 @@
         <v>11</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" t="s">
         <v>137</v>
@@ -2156,7 +2157,7 @@
         <v>11</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G41" t="s">
         <v>140</v>
@@ -2179,7 +2180,7 @@
         <v>11</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G42" t="s">
         <v>143</v>
@@ -2225,7 +2226,7 @@
         <v>11</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G44" t="s">
         <v>149</v>
@@ -2248,7 +2249,7 @@
         <v>11</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
         <v>152</v>
@@ -2271,7 +2272,7 @@
         <v>11</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G46" t="s">
         <v>155</v>
@@ -2317,7 +2318,7 @@
         <v>11</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G48" t="s">
         <v>161</v>
@@ -2340,7 +2341,7 @@
         <v>11</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G49" t="s">
         <v>164</v>
@@ -2363,7 +2364,7 @@
         <v>11</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G50" t="s">
         <v>167</v>
@@ -2386,7 +2387,7 @@
         <v>11</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G51" t="s">
         <v>170</v>
@@ -2409,7 +2410,7 @@
         <v>11</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G52" t="s">
         <v>173</v>
@@ -2432,7 +2433,7 @@
         <v>11</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G53" t="s">
         <v>176</v>
@@ -2455,7 +2456,7 @@
         <v>11</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G54" t="s">
         <v>179</v>
@@ -2478,7 +2479,7 @@
         <v>11</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" t="s">
         <v>182</v>
@@ -2501,7 +2502,7 @@
         <v>11</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G56" t="s">
         <v>185</v>
@@ -2521,10 +2522,10 @@
         <v>187</v>
       </c>
       <c r="E57" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F57">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G57" t="s">
         <v>188</v>
@@ -2547,7 +2548,7 @@
         <v>11</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G58" t="s">
         <v>191</v>
@@ -2570,7 +2571,7 @@
         <v>11</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="s">
         <v>194</v>
@@ -2593,7 +2594,7 @@
         <v>11</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G60" t="s">
         <v>197</v>
@@ -2639,7 +2640,7 @@
         <v>11</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" t="s">
         <v>203</v>
@@ -2662,7 +2663,7 @@
         <v>11</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G63" t="s">
         <v>206</v>
@@ -2685,7 +2686,7 @@
         <v>11</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G64" t="s">
         <v>209</v>
@@ -2708,7 +2709,7 @@
         <v>11</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G65" t="s">
         <v>212</v>
@@ -2731,7 +2732,7 @@
         <v>11</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s">
         <v>215</v>
@@ -2754,7 +2755,7 @@
         <v>11</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G67" t="s">
         <v>218</v>
@@ -2777,7 +2778,7 @@
         <v>11</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G68" t="s">
         <v>221</v>
@@ -2800,7 +2801,7 @@
         <v>11</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G69" t="s">
         <v>224</v>
@@ -2820,10 +2821,10 @@
         <v>226</v>
       </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G70" t="s">
         <v>227</v>
@@ -2846,7 +2847,7 @@
         <v>11</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G71" t="s">
         <v>230</v>
@@ -2869,7 +2870,7 @@
         <v>11</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G72" t="s">
         <v>233</v>
@@ -2892,7 +2893,7 @@
         <v>11</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
         <v>236</v>
@@ -2915,7 +2916,7 @@
         <v>11</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G74" t="s">
         <v>239</v>
@@ -2938,7 +2939,7 @@
         <v>11</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G75" t="s">
         <v>243</v>
@@ -2961,7 +2962,7 @@
         <v>11</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G76" t="s">
         <v>246</v>
@@ -3007,7 +3008,7 @@
         <v>11</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" t="s">
         <v>252</v>
@@ -3050,7 +3051,7 @@
         <v>257</v>
       </c>
       <c r="E80" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3073,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="E81" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3096,7 +3097,7 @@
         <v>263</v>
       </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -3122,7 +3123,7 @@
         <v>11</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G83" t="s">
         <v>267</v>
@@ -3142,7 +3143,7 @@
         <v>269</v>
       </c>
       <c r="E84" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -3168,7 +3169,7 @@
         <v>11</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G85" t="s">
         <v>273</v>
@@ -3191,7 +3192,7 @@
         <v>11</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G86" t="s">
         <v>276</v>
@@ -3214,7 +3215,7 @@
         <v>11</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G87" t="s">
         <v>279</v>
@@ -3237,7 +3238,7 @@
         <v>11</v>
       </c>
       <c r="F88">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G88" t="s">
         <v>282</v>
@@ -3283,7 +3284,7 @@
         <v>11</v>
       </c>
       <c r="F90">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="G90" t="s">
         <v>288</v>

--- a/datos/catalogo.xlsx
+++ b/datos/catalogo.xlsx
@@ -2111,7 +2111,7 @@
         <v>11</v>
       </c>
       <c r="F39">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G39" t="s">
         <v>134</v>
@@ -2131,10 +2131,7 @@
         <v>136</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G40" t="s">
         <v>137</v>
@@ -2157,7 +2154,7 @@
         <v>11</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G41" t="s">
         <v>140</v>
